--- a/inspirational_quotes.xlsx
+++ b/inspirational_quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF390DCF-49CD-41EE-A2BC-46C4BEDD36D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14FB2BF-AB2E-463A-B15F-D4B989869E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -328,7 +328,7 @@
     <t>author</t>
   </si>
   <si>
-    <t>quotes</t>
+    <t>quote</t>
   </si>
 </sst>
 </file>

--- a/inspirational_quotes.xlsx
+++ b/inspirational_quotes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sivane\Desktop\ai-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14FB2BF-AB2E-463A-B15F-D4B989869E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE2D00D-C7CB-412F-93E3-C48819AC4C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="20" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,13 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="103">
-  <si>
-    <t>אם אתם רוצים להיות מאושרים, הציבו לעצמכם מטרה, שחררו לחופשי את האנרגיה שלכם, והיו מלאי השראה ותקווה</t>
-  </si>
-  <si>
-    <t>אנדרו קרנגי</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="101">
   <si>
     <t>אם אתם מתחילים לחשוב שהבעיה נמצאת 'שם', עצרו מיד. הבעיה האמיתית היא עצם המחשבה הזו</t>
   </si>
@@ -671,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="91.1640625" bestFit="1" customWidth="1"/>
@@ -680,10 +674,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -891,23 +885,23 @@
         <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
         <v>53</v>
-      </c>
-      <c r="B29" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -939,15 +933,15 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" t="s">
         <v>62</v>
-      </c>
-      <c r="B34" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -1092,14 +1086,6 @@
       </c>
       <c r="B52" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>99</v>
-      </c>
-      <c r="B53" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
